--- a/artfynd/A 21219-2026 artfynd.xlsx
+++ b/artfynd/A 21219-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118237707</v>
+        <v>118237699</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526330</v>
+        <v>526293</v>
       </c>
       <c r="R2" t="n">
-        <v>6980645</v>
+        <v>6980809</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118237706</v>
+        <v>118237707</v>
       </c>
       <c r="B3" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526237</v>
+        <v>526330</v>
       </c>
       <c r="R3" t="n">
-        <v>6980802</v>
+        <v>6980645</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118237699</v>
+        <v>118237706</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526293</v>
+        <v>526237</v>
       </c>
       <c r="R4" t="n">
-        <v>6980809</v>
+        <v>6980802</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 21219-2026 artfynd.xlsx
+++ b/artfynd/A 21219-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118237699</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118237707</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118237706</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>